--- a/files/register_testcases.xlsx
+++ b/files/register_testcases.xlsx
@@ -471,32 +471,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abcd1</t>
+          <t>UserOne1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aa123456</t>
+          <t>StrongPwd1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aa123456</t>
+          <t>StrongPwd1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>test1@example.com</t>
+          <t>user01@test.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13800000001</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>所有字段有效</t>
+          <t>所有字段均符合注册规则</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abcdefghij1234567890</t>
+          <t>Test_2345</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Password123</t>
+          <t>HelloWorld9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Password123</t>
+          <t>HelloWorld9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user2@mail.com</t>
+          <t>user02@example.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13900000002</t>
+          <t>15912345608</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>所有字段有效且边界内</t>
+          <t>包含下划线的合法账号及合法密码</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1Abc</t>
+          <t>Abcd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>u3@test.cn</t>
+          <t>mini@test.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13700000003</t>
+          <t>13612345601</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>账号以数字开头</t>
+          <t>账号长度取最小合法边界4且密码长度取最小合法边界8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>注册失败提示账号格式错误</t>
+          <t>注册成功</t>
         </is>
       </c>
     </row>
@@ -612,42 +612,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ValidName</t>
+          <t>A1234567890123456789</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abcdef1234</t>
+          <t>Abcd1234Efgh5678IJKL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>abcdef1234</t>
+          <t>Abcd1234Efgh5678IJKL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user4@test.com</t>
+          <t>longmax@example.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13600000004</t>
+          <t>19912345601</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>密码缺少大写字母</t>
+          <t>账号长度取最大合法边界20且密码长度取最大合法边界20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>注册失败提示密码必须包含大写字母</t>
+          <t>注册成功</t>
         </is>
       </c>
     </row>
@@ -659,42 +659,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ValidAcct5</t>
+          <t>Abc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Goodpass123</t>
+          <t>Qwer1234</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Badpass123</t>
+          <t>Qwer1234</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>user5@mail.com</t>
+          <t>shortacc@test.org</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13500000005</t>
+          <t>13312345602</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>确认密码与密码不一致</t>
+          <t>账号长度为3低于最小合法值4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>注册失败提示两次密码不一致</t>
+          <t>注册失败账号长度不能少于4位</t>
         </is>
       </c>
     </row>
@@ -706,42 +706,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abc1</t>
+          <t>B12345678901234567890</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abcd1234</t>
+          <t>TigerKing9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abcd1234</t>
+          <t>TigerKing9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>u6@example.com</t>
+          <t>acc21@example.net</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13400000006</t>
+          <t>13712345603</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>账号长度最小合法值4位且密码长度8位</t>
+          <t>账号长度为21高于最大合法值20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>健壮边界值(合法边界)</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>注册成功</t>
+          <t>注册失败账号长度不能超过20位</t>
         </is>
       </c>
     </row>
@@ -753,42 +753,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abcdef12345678901234</t>
+          <t>UserLower1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aabcdefghij123456789</t>
+          <t>abcd1234</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aabcdefghij123456789</t>
+          <t>abcd1234</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>user7@example.org</t>
+          <t>nocc@test.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13300000007</t>
+          <t>13512345604</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>账号长度最大合法值20位且密码长度20位</t>
+          <t>密码只含小写字母和数字缺少大写字母</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>健壮边界值(合法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>注册成功</t>
+          <t>注册失败密码必须包含大写字母</t>
         </is>
       </c>
     </row>
@@ -800,42 +800,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ab1</t>
+          <t>Mismatch1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aa1234567</t>
+          <t>Correct5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aa1234567</t>
+          <t>Wrong9999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>u8@sample.com</t>
+          <t>mismatch@test.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13200000008</t>
+          <t>18812345605</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>账号长度仅为3位小于最小边界</t>
+          <t>确认密码与密码输入不一致</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>注册失败提示账号长度4到20位</t>
+          <t>注册失败两次输入的密码不一致</t>
         </is>
       </c>
     </row>
@@ -847,42 +847,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Account9</t>
+          <t>EmailBad1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Abc1234</t>
+          <t>Mail1234</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Abc1234</t>
+          <t>Mail1234</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>user9@demo.com</t>
+          <t>bad-email</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13100000009</t>
+          <t>18712345606</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>密码长度仅为7位小于最小边界</t>
+          <t>邮箱地址缺少@符号和域名</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>注册失败提示密码长度8到20位</t>
+          <t>注册失败邮箱格式不正确</t>
         </is>
       </c>
     </row>
@@ -894,42 +894,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Account10</t>
+          <t>PhoneBad1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aabcdefghij1234567890</t>
+          <t>CallMe01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aabcdefghij1234567890</t>
+          <t>CallMe01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>user10@test.net</t>
+          <t>phone@example.cn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13000000010</t>
+          <t>21234567890</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>密码长度为21位大于最大边界</t>
+          <t>手机号不是以1开头</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>注册失败提示密码长度8到20位</t>
+          <t>注册失败手机号必须以1开头</t>
         </is>
       </c>
     </row>

--- a/files/register_testcases.xlsx
+++ b/files/register_testcases.xlsx
@@ -471,32 +471,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UserOne1</t>
+          <t>Alpha_001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>StrongPwd1</t>
+          <t>Pwd12345A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>StrongPwd1</t>
+          <t>Pwd12345A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user01@test.com</t>
+          <t>alpha001@test.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13800138001</t>
+          <t>13800000001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>所有字段均符合注册规则</t>
+          <t>全部字段合法且账号含下划线</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Test_2345</t>
+          <t>A1b2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HelloWorld9</t>
+          <t>Abc12345</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HelloWorld9</t>
+          <t>Abc12345</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user02@example.com</t>
+          <t>min4@test.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15912345608</t>
+          <t>13900000002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>包含下划线的合法账号及合法密码</t>
+          <t>账号长度4位且密码长度8位合法边界</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>有效等价类</t>
+          <t>健壮边界值(合法边界)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -565,32 +565,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abcd</t>
+          <t>Abcdefghij1234567890</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abcdef12</t>
+          <t>Abcdef1234567890XYZW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Abcdef12</t>
+          <t>Abcdef1234567890XYZW</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mini@test.com</t>
+          <t>max20@test.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13612345601</t>
+          <t>13700000003</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>账号长度取最小合法边界4且密码长度取最小合法边界8</t>
+          <t>账号长度20位且密码长度20位合法边界</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,42 +612,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A1234567890123456789</t>
+          <t>1abcd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Abcd1234Efgh5678IJKL</t>
+          <t>Zxcv1234</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Abcd1234Efgh5678IJKL</t>
+          <t>Zxcv1234</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>longmax@example.com</t>
+          <t>digitstart@test.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19912345601</t>
+          <t>13600000004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>账号长度取最大合法边界20且密码长度取最大合法边界20</t>
+          <t>账号以数字开头</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>健壮边界值(合法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>注册成功</t>
+          <t>注册失败 提示账号需字母开头</t>
         </is>
       </c>
     </row>
@@ -659,42 +659,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abc</t>
+          <t>GoodUser5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Qwer1234</t>
+          <t>pass1234</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Qwer1234</t>
+          <t>pass1234</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>shortacc@test.org</t>
+          <t>nocap@test.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13312345602</t>
+          <t>13500000005</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>账号长度为3低于最小合法值4</t>
+          <t>密码不含大写字母</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>注册失败账号长度不能少于4位</t>
+          <t>注册失败 提示密码需包含大写字母小写字母和数字</t>
         </is>
       </c>
     </row>
@@ -706,42 +706,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B12345678901234567890</t>
+          <t>ValidUser6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TigerKing9</t>
+          <t>Qwer1234</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TigerKing9</t>
+          <t>Qwer1235</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>acc21@example.net</t>
+          <t>mismatch@test.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13712345603</t>
+          <t>13400000006</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>账号长度为21高于最大合法值20</t>
+          <t>确认密码与密码不一致</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>健壮边界值(非法边界)</t>
+          <t>无效等价类</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>注册失败账号长度不能超过20位</t>
+          <t>注册失败 提示两次密码不一致</t>
         </is>
       </c>
     </row>
@@ -753,32 +753,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UserLower1</t>
+          <t>EmailUser7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abcd1234</t>
+          <t>Plok1234</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>abcd1234</t>
+          <t>Plok1234</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>nocc@test.com</t>
+          <t>emailuser7.test.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13512345604</t>
+          <t>13300000007</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>密码只含小写字母和数字缺少大写字母</t>
+          <t>邮箱缺少@符号</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>注册失败密码必须包含大写字母</t>
+          <t>注册失败 提示邮箱格式错误</t>
         </is>
       </c>
     </row>
@@ -800,42 +800,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mismatch1</t>
+          <t>Abc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Correct5</t>
+          <t>Asdf1234</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wrong9999</t>
+          <t>Asdf1234</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>mismatch@test.com</t>
+          <t>shortacc@test.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18812345605</t>
+          <t>13200000008</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>确认密码与密码输入不一致</t>
+          <t>账号长度3位小于最小4位</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>注册失败两次输入的密码不一致</t>
+          <t>注册失败 提示账号长度4到20位</t>
         </is>
       </c>
     </row>
@@ -847,42 +847,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EmailBad1</t>
+          <t>ShortPwd9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mail1234</t>
+          <t>Abc1234</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mail1234</t>
+          <t>Abc1234</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>bad-email</t>
+          <t>shortpwd@test.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18712345606</t>
+          <t>13100000009</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>邮箱地址缺少@符号和域名</t>
+          <t>密码长度7位小于最小8位</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>注册失败邮箱格式不正确</t>
+          <t>注册失败 提示密码长度8到20位</t>
         </is>
       </c>
     </row>
@@ -894,42 +894,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PhoneBad1</t>
+          <t>MobileUser10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CallMe01</t>
+          <t>Qaz12345</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CallMe01</t>
+          <t>Qaz12345</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>phone@example.cn</t>
+          <t>mobile10@test.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21234567890</t>
+          <t>1300000010</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>手机号不是以1开头</t>
+          <t>手机号长度10位小于11位</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>无效等价类</t>
+          <t>健壮边界值(非法边界)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>注册失败手机号必须以1开头</t>
+          <t>注册失败 提示手机号需1开头11位</t>
         </is>
       </c>
     </row>
